--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/ZoneAffix.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/ZoneAffix.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Comum</t>
+          <t>sem graça</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Caprichoso</t>
+          <t>caprichoso</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Impuro</t>
+          <t>contaminado</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Esquecido</t>
+          <t>esquecido</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ancestral</t>
+          <t>antigo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Selvagem</t>
+          <t>selvagem</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Espiritual</t>
+          <t>espiritual</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Melancólico</t>
+          <t>melancólico</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Perigoso</t>
+          <t>perigoso</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Do Engano</t>
+          <t>emaranhado</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Encantador</t>
+          <t>fascinante</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estranho</t>
+          <t>estranho</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Trágico</t>
+          <t>trágico</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sinistro</t>
+          <t>sinistro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Arrepiante</t>
+          <t>gélido</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Aterrorizante</t>
+          <t>aterrorizante</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Coberto de Musgo</t>
+          <t>musgoso</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Velho</t>
+          <t>velho</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Úmido</t>
+          <t>úmido</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Histórico</t>
+          <t>histórico</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Desconhecido</t>
+          <t>desconhecido</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tradicional</t>
+          <t>tradicional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sem Nome</t>
+          <t>sem nome</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Distorcido</t>
+          <t>distorcido</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Proibido</t>
+          <t>proibido</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Silencioso</t>
+          <t>silencioso</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nebuloso</t>
+          <t>enevoado</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sombrio</t>
+          <t>escuro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Encantado</t>
+          <t>encantado</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Místico</t>
+          <t>místico</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Blasfemo</t>
+          <t>blasfemo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arruinado</t>
+          <t>arruinado</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Desmoronando</t>
+          <t>desmoronando</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Isolado</t>
+          <t>isolado</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arcano</t>
+          <t>arcano</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Animado</t>
+          <t>animado</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rústico</t>
+          <t>rústico</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Guia</t>
+          <t>orientador</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Terroso</t>
+          <t>terroso</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Protegido</t>
+          <t>resguardado</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
